--- a/GameConfig/Datas/skill.xlsx
+++ b/GameConfig/Datas/skill.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3114fccc97ea45fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd99d8a1add04f24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -530,9 +530,19 @@
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="2">
+  <x:cellXfs count="4">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="22">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="49">
     <x:cellStyle name="常规" xfId="0"/>
@@ -654,6 +664,23 @@
     </x:indexedColors>
   </x:colors>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -850,49 +877,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">skillType</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">behaviorType</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">intValues</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">floatValues</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">requiresTarget</x:t>
-        </x:is>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="1" t="str">
+        <x:v>##var</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="str">
+        <x:v>id</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="str">
+        <x:v>name</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="str">
+        <x:v>skillType</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="str">
+        <x:v>behaviorType</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="str">
+        <x:v>requiresTarget</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="str">
+        <x:v>maxLevel</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="1" t="str">
+        <x:v>##var</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -901,115 +920,73 @@
       <x:c r="F2" s="1"/>
       <x:c r="G2" s="1"/>
     </x:row>
-    <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(array#sep=,),int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(array#sep=,),float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bool</x:t>
-        </x:is>
+    <x:row r="3" ht="30" customHeight="1">
+      <x:c r="A3" s="1" t="str">
+        <x:v>##type</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="str">
+        <x:v>int</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##group</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">c</x:t>
-        </x:is>
+    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="A4" s="1" t="str">
+        <x:v>##group</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>c</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="str">
+        <x:v>c</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">技能唯一ID</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1主动2被动</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">行为注册名</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">整数参数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">浮点参数</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">是否需要目标</x:t>
-        </x:is>
+    <x:row r="5" ht="66" customHeight="1">
+      <x:c r="A5" s="3" t="str">
+        <x:v>##</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="str">
+        <x:v>技能唯一ID</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="str">
+        <x:v>技能名称</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="str">
+        <x:v>1主动2被动</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="str">
+        <x:v>行为注册名</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="str">
+        <x:v>是否需要目标实体</x:v>
+      </x:c>
+      <x:c r="G5" s="3" t="str">
+        <x:v>最高技能等级（须有对应等级记录）</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
@@ -1017,29 +994,23 @@
       <x:c r="B6" s="1" t="n">
         <x:v>1505</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="n">
+      <x:c r="C6" s="1" t="str">
+        <x:v>寒霜炮击</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">DamageThenApplySlow</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E6" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">0.3,3</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="1" t="b">
+      <x:c r="E6" s="1" t="str">
+        <x:v>DamageThenApplySlow</x:v>
+      </x:c>
+      <x:c r="F6" s="2" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.3" header="0.3" footer="0.3"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>